--- a/data/trans_orig/P57B3_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57B3_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido solo/a en 2023</t>
+          <t>Población según se ha sentido solo/a en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20988</t>
+          <t>22538</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42473</t>
+          <t>43104</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25344</t>
+          <t>25106</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41272</t>
+          <t>41279</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51638</t>
+          <t>51639</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77736</t>
+          <t>77857</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41791</t>
+          <t>43093</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68050</t>
+          <t>69645</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58654</t>
+          <t>57773</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82843</t>
+          <t>83955</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108159</t>
+          <t>106586</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>144538</t>
+          <t>143396</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>174419</t>
+          <t>171675</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>225282</t>
+          <t>223969</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>198626</t>
+          <t>197451</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>236838</t>
+          <t>234683</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>383390</t>
+          <t>383700</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>446511</t>
+          <t>446019</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>323823</t>
+          <t>324870</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>378076</t>
+          <t>380612</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>333525</t>
+          <t>336346</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>376481</t>
+          <t>376006</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>672683</t>
+          <t>671232</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>741449</t>
+          <t>741386</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,61%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43218</t>
+          <t>44100</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>694643</t>
+          <t>771426</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29789</t>
+          <t>30633</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51264</t>
+          <t>54754</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>82671</t>
+          <t>81603</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>906550</t>
+          <t>964640</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>44,89%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41456</t>
+          <t>38614</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100809</t>
+          <t>100602</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94126</t>
+          <t>94256</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>126708</t>
+          <t>126081</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116622</t>
+          <t>118556</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>214382</t>
+          <t>213801</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>184924</t>
+          <t>151536</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>426808</t>
+          <t>425454</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>319044</t>
+          <t>318835</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>368660</t>
+          <t>368465</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>455023</t>
+          <t>433634</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>767166</t>
+          <t>771038</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>273313</t>
+          <t>241801</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>652847</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>440289</t>
+          <t>439565</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>493618</t>
+          <t>493475</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664142</t>
+          <t>667023</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1115285</t>
+          <t>1120975</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>52,17%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11093</t>
+          <t>9967</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29458</t>
+          <t>26592</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8651</t>
+          <t>8862</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29976</t>
+          <t>28862</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24126</t>
+          <t>23693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51921</t>
+          <t>52164</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33871</t>
+          <t>35315</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>62937</t>
+          <t>63038</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23351</t>
+          <t>21041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>65203</t>
+          <t>64004</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>59947</t>
+          <t>60293</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>117190</t>
+          <t>116764</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>212872</t>
+          <t>214067</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>274204</t>
+          <t>274912</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>128555</t>
+          <t>117595</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>317268</t>
+          <t>319123</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,17 +2159,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>480256</t>
+          <t>480255</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>315885</t>
+          <t>289098</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>562491</t>
+          <t>566448</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,62%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>364151</t>
+          <t>364892</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>426806</t>
+          <t>426087</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>528674</t>
+          <t>530222</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>764436</t>
+          <t>784371</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>922080</t>
+          <t>921645</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1230080</t>
+          <t>1265087</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>77,32%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28388</t>
+          <t>28901</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50591</t>
+          <t>50119</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35568</t>
+          <t>36777</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59358</t>
+          <t>60693</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>71442</t>
+          <t>69804</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>105821</t>
+          <t>103925</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51539</t>
+          <t>50817</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>79585</t>
+          <t>77648</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62155</t>
+          <t>61004</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95035</t>
+          <t>95009</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>121728</t>
+          <t>120640</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>164745</t>
+          <t>163533</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>239133</t>
+          <t>239314</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>299780</t>
+          <t>297001</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>268793</t>
+          <t>264948</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>372393</t>
+          <t>372800</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>536649</t>
+          <t>532643</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>654855</t>
+          <t>652031</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>525530</t>
+          <t>524194</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>588088</t>
+          <t>587115</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>586077</t>
+          <t>587810</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>722829</t>
+          <t>731987</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1134313</t>
+          <t>1136649</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1282177</t>
+          <t>1285679</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,66%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>127244</t>
+          <t>126748</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1040145</t>
+          <t>1119406</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>114171</t>
+          <t>112890</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>160826</t>
+          <t>159945</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>261836</t>
+          <t>263767</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1454463</t>
+          <t>1372465</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>184248</t>
+          <t>184640</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>275812</t>
+          <t>273593</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>249101</t>
+          <t>245828</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>334553</t>
+          <t>337159</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>469975</t>
+          <t>470160</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>595762</t>
+          <t>592055</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>823630</t>
+          <t>818316</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1137197</t>
+          <t>1133051</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>933543</t>
+          <t>939586</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1224976</t>
+          <t>1225748</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1884033</t>
+          <t>1867144</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2313594</t>
+          <t>2325161</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1401663</t>
+          <t>1350780</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1976983</t>
+          <t>1979854</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1958955</t>
+          <t>1959813</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2380505</t>
+          <t>2344653</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3463186</t>
+          <t>3482742</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4153567</t>
+          <t>4132562</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B3_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57B3_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>31088</t>
+          <t>34914</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22538</t>
+          <t>24558</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43104</t>
+          <t>46247</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>32404</t>
+          <t>36130</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25106</t>
+          <t>28294</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41279</t>
+          <t>46039</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>63492</t>
+          <t>71044</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51639</t>
+          <t>57072</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77857</t>
+          <t>87176</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>54849</t>
+          <t>58650</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43093</t>
+          <t>45724</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69645</t>
+          <t>74807</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>69559</t>
+          <t>75547</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57773</t>
+          <t>63712</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83955</t>
+          <t>88762</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>124408</t>
+          <t>134197</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106586</t>
+          <t>117005</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>143396</t>
+          <t>153967</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>197506</t>
+          <t>213862</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>171675</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>223969</t>
+          <t>238725</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>215649</t>
+          <t>235560</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>197451</t>
+          <t>216220</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>234683</t>
+          <t>257227</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>413155</t>
+          <t>449422</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>383700</t>
+          <t>419602</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>446019</t>
+          <t>483668</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>351998</t>
+          <t>383284</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>324870</t>
+          <t>355289</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>380612</t>
+          <t>411136</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>356500</t>
+          <t>384142</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>336346</t>
+          <t>361882</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>376006</t>
+          <t>404973</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>708499</t>
+          <t>767425</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>671232</t>
+          <t>730065</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>741386</t>
+          <t>801932</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,39%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>674111</t>
+          <t>731379</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>674111</t>
+          <t>731379</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>674111</t>
+          <t>731379</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1309553</t>
+          <t>1422088</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1309553</t>
+          <t>1422088</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1309553</t>
+          <t>1422088</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>283190</t>
+          <t>49684</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44100</t>
+          <t>38296</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>771426</t>
+          <t>66039</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38789</t>
+          <t>45809</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30633</t>
+          <t>35147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54754</t>
+          <t>58670</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>321979</t>
+          <t>95493</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>81603</t>
+          <t>79665</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>964640</t>
+          <t>113984</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>73430</t>
+          <t>83113</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38614</t>
+          <t>66986</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100602</t>
+          <t>102187</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,67 +1442,67 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>108842</t>
+          <t>125415</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94256</t>
+          <t>107524</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>126081</t>
+          <t>143989</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>10,05%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>13,46%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>208528</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>184261</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>234749</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>9,85%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>13,17%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>182273</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>118556</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>213801</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>8,48%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>326514</t>
+          <t>354881</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151536</t>
+          <t>322034</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>425454</t>
+          <t>388831</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>342927</t>
+          <t>381691</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>318835</t>
+          <t>352781</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>368465</t>
+          <t>407377</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>669441</t>
+          <t>736572</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>689113</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>771038</t>
+          <t>780385</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>508705</t>
+          <t>560086</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>241801</t>
+          <t>523996</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>596290</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>466497</t>
+          <t>516774</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>439565</t>
+          <t>490288</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>493475</t>
+          <t>547675</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>975202</t>
+          <t>1076860</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>667023</t>
+          <t>1030675</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1120975</t>
+          <t>1126938</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>53,22%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1191839</t>
+          <t>1047763</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1191839</t>
+          <t>1047763</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1191839</t>
+          <t>1047763</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>957056</t>
+          <t>1069690</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>957056</t>
+          <t>1069690</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>957056</t>
+          <t>1069690</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2148895</t>
+          <t>2117453</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2148895</t>
+          <t>2117453</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2148895</t>
+          <t>2117453</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>17479</t>
+          <t>19670</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>12605</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26592</t>
+          <t>31093</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>19674</t>
+          <t>21704</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>15039</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28862</t>
+          <t>31747</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>37153</t>
+          <t>41374</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23693</t>
+          <t>30670</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52164</t>
+          <t>53824</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46920</t>
+          <t>52323</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35315</t>
+          <t>39543</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>63038</t>
+          <t>69206</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44910</t>
+          <t>53297</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21041</t>
+          <t>41186</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>64004</t>
+          <t>68018</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>91830</t>
+          <t>105620</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>60293</t>
+          <t>85886</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>116764</t>
+          <t>128441</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>242782</t>
+          <t>283378</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>214067</t>
+          <t>252288</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>274912</t>
+          <t>316395</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>237474</t>
+          <t>279225</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>117595</t>
+          <t>254177</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>319123</t>
+          <t>304512</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>480255</t>
+          <t>562604</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>289098</t>
+          <t>521515</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>566448</t>
+          <t>603157</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>37,39%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>396633</t>
+          <t>446773</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>364892</t>
+          <t>415025</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>426087</t>
+          <t>478220</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>630216</t>
+          <t>456849</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>530222</t>
+          <t>430875</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>784371</t>
+          <t>483630</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1026848</t>
+          <t>903623</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>921645</t>
+          <t>861951</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1265087</t>
+          <t>944275</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>58,53%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>703813</t>
+          <t>802145</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>703813</t>
+          <t>802145</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>703813</t>
+          <t>802145</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>932274</t>
+          <t>811075</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>932274</t>
+          <t>811075</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>932274</t>
+          <t>811075</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1636087</t>
+          <t>1613221</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1636087</t>
+          <t>1613221</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1636087</t>
+          <t>1613221</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>38416</t>
+          <t>43913</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28901</t>
+          <t>33141</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50119</t>
+          <t>56700</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>47320</t>
+          <t>56908</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36777</t>
+          <t>46308</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60693</t>
+          <t>70167</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>85736</t>
+          <t>100821</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>69804</t>
+          <t>85508</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>103925</t>
+          <t>120721</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>63962</t>
+          <t>74773</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50817</t>
+          <t>60089</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>77648</t>
+          <t>91465</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>78992</t>
+          <t>89996</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61004</t>
+          <t>74666</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95009</t>
+          <t>106183</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>142954</t>
+          <t>164769</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>120640</t>
+          <t>144556</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>163533</t>
+          <t>188739</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>267843</t>
+          <t>292292</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>239314</t>
+          <t>264853</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>297001</t>
+          <t>323597</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>335663</t>
+          <t>357321</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>264948</t>
+          <t>329930</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>372800</t>
+          <t>385644</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>603506</t>
+          <t>649614</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>532643</t>
+          <t>608463</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>652031</t>
+          <t>693309</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -2771,102 +2771,102 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>556610</t>
+          <t>579084</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>524194</t>
+          <t>541935</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>587115</t>
+          <t>608387</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>54,74%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>61,45%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>612691</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>584319</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>643384</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>54,86%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>52,32%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>57,6%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1393</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1191775</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>1149839</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>1237974</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>56,56%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>63,35%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>827</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>630917</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>587810</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>731987</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>57,73%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>53,78%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>66,98%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1393</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1187527</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>1136649</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>1285679</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>58,8%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>58,76%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1092891</t>
+          <t>1116916</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1092891</t>
+          <t>1116916</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1092891</t>
+          <t>1116916</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2019723</t>
+          <t>2106978</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2019723</t>
+          <t>2106978</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2019723</t>
+          <t>2106978</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>370173</t>
+          <t>148181</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>126748</t>
+          <t>126418</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1119406</t>
+          <t>173837</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>138186</t>
+          <t>160551</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>112890</t>
+          <t>141049</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>159945</t>
+          <t>182927</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
           <t>3,78%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>508360</t>
+          <t>308731</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>263767</t>
+          <t>277260</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1372465</t>
+          <t>342071</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>239160</t>
+          <t>268859</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>184640</t>
+          <t>239458</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>273593</t>
+          <t>309049</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>302304</t>
+          <t>344256</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>245828</t>
+          <t>316348</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>337159</t>
+          <t>378300</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>541464</t>
+          <t>613115</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>470160</t>
+          <t>570572</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>592055</t>
+          <t>658392</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1034644</t>
+          <t>1144414</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>818316</t>
+          <t>1084585</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1133051</t>
+          <t>1212257</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1131713</t>
+          <t>1253798</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>939586</t>
+          <t>1204006</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1225748</t>
+          <t>1307051</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2166357</t>
+          <t>2398212</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1867144</t>
+          <t>2320272</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2325161</t>
+          <t>2478695</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>34,14%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1813946</t>
+          <t>1969227</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1350780</t>
+          <t>1897038</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1979854</t>
+          <t>2033875</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2084130</t>
+          <t>1970455</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1959813</t>
+          <t>1913517</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2344653</t>
+          <t>2019294</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3898076</t>
+          <t>3939682</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3482742</t>
+          <t>3850363</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4132562</t>
+          <t>4021284</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>55,39%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3457924</t>
+          <t>3530680</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3457924</t>
+          <t>3530680</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3457924</t>
+          <t>3530680</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3656333</t>
+          <t>3729060</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3656333</t>
+          <t>3729060</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3656333</t>
+          <t>3729060</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7114257</t>
+          <t>7259740</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7114257</t>
+          <t>7259740</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7114257</t>
+          <t>7259740</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
